--- a/backtest_runs/20260410_193731/by_symbol/MSOT/MSOT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MSOT/MSOT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-8785</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>91215</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>91215</v>
@@ -955,7 +955,7 @@
         <v>-8380.890000000005</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>96117.03</v>
@@ -1093,7 +1093,7 @@
         <v>-1844.850000000007</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>104287.08</v>
@@ -1231,7 +1231,7 @@
         <v>-351.400000000005</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>116375.24</v>
@@ -1277,7 +1277,7 @@
         <v>-5885.950000000003</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>110489.29</v>
@@ -1415,7 +1415,7 @@
         <v>-11719.19000000002</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>111561.06</v>
@@ -1461,7 +1461,7 @@
         <v>-8205.189999999991</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>103355.87</v>
@@ -1645,7 +1645,7 @@
         <v>-2986.899999999992</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>113282.92</v>
